--- a/artfynd/A 52212-2025 artfynd.xlsx
+++ b/artfynd/A 52212-2025 artfynd.xlsx
@@ -10236,7 +10236,7 @@
         <v>133185133</v>
       </c>
       <c r="B95" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
